--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-22.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-22.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261020" sheetId="1" r:id="R9f2e9314d37b4512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261021" sheetId="1" r:id="R96d7cebcaaac4ef1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <x:si>
-    <x:t>Daily Holdings (%)  10/20/2026</x:t>
+    <x:t>Daily Holdings (%)  10/21/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>64,292,356</x:t>
+    <x:t>64,472,781</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$13,917,366,303.32</x:t>
+    <x:t>$14,311,023,198.57</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.44%</x:t>
+    <x:t>20.56%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,31 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,362,522</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,530,300,851.76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.59%</x:t>
+    <x:t>15,405,635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,653,539,700.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.56%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Advanced Micro Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BBQCY0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6,918,432</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,823,955,735.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.49%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -94,31 +112,13 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>11,218,028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,750,972,022.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.51%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Advanced Micro Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BBQCY0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6,899,070</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,689,208,691.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.42%</x:t>
+    <x:t>11,249,584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,800,109,475.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.46%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -130,13 +130,13 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,340,569</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,427,963,256.82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.03%</x:t>
+    <x:t>12,375,282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,522,624,021.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.06%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -148,13 +148,31 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,497,930</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,134,390,135.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.60%</x:t>
+    <x:t>3,507,744</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,204,920,460.48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.61%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,762,516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,151,270,995.36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.53%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -166,31 +184,13 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>12,826,847</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,083,830,555.74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.53%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,740,746</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,073,463,199.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.51%</x:t>
+    <x:t>12,862,841</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,148,308,963.16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.52%</x:t>
   </x:si>
   <x:si>
     <x:t>ASML</x:t>
@@ -202,13 +202,10 @@
     <x:t>BBG000K6MRN4</x:t>
   </x:si>
   <x:si>
-    <x:t>1,870,779</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,050,941,224.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.48%</x:t>
+    <x:t>1,876,029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,145,519,064.01</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -220,13 +217,31 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>17,648,978</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,854,545,701.72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.19%</x:t>
+    <x:t>17,698,622</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,892,485,793.46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.16%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Intel Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C0G1D1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,471,090</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,832,592,526.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.07%</x:t>
   </x:si>
   <x:si>
     <x:t>AMAT</x:t>
@@ -238,31 +253,31 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>6,885,310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,788,412,843.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.10%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Intel Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C0G1D1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,385,620</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,786,057,497.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.09%</x:t>
+    <x:t>6,904,679</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,823,599,430.26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.06%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qualcomm Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000CGC1X8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,366,880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,734,689,964.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.93%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -274,28 +289,13 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,220,918</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,692,700,847.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qualcomm Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000CGC1X8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,323,781</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,692,541,559.51</x:t>
+    <x:t>10,249,667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,673,215,650.27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.84%</x:t>
   </x:si>
   <x:si>
     <x:t>SKHY</x:t>
@@ -307,13 +307,13 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>18,099,306</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,530,101,985.74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.72%</x:t>
+    <x:t>18,150,098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,600,001,538.50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.74%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -325,10 +325,10 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,399,347</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,407,219,124.89</x:t>
+    <x:t>4,411,723</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,438,530,518.61</x:t>
   </x:si>
   <x:si>
     <x:t>2.07%</x:t>
@@ -343,13 +343,13 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,099,099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,387,218,694.38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.04%</x:t>
+    <x:t>3,107,814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,402,214,598.66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.01%</x:t>
   </x:si>
   <x:si>
     <x:t>MPWR</x:t>
@@ -361,13 +361,13 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>668,755</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$835,101,118.70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.23%</x:t>
+    <x:t>670,638</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$860,643,158.16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.24%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -379,13 +379,13 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,374,147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$799,114,138.73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.17%</x:t>
+    <x:t>2,380,825</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$822,551,229.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.18%</x:t>
   </x:si>
   <x:si>
     <x:t>NXPI</x:t>
@@ -397,10 +397,10 @@
     <x:t>BBG000BND699</x:t>
   </x:si>
   <x:si>
-    <x:t>3,236,432</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$768,976,243.20</x:t>
+    <x:t>3,245,532</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$786,587,135.52</x:t>
   </x:si>
   <x:si>
     <x:t>1.13%</x:t>
@@ -415,10 +415,10 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,394,960</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$682,084,608.00</x:t>
+    <x:t>2,401,694</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$696,635,361.64</x:t>
   </x:si>
   <x:si>
     <x:t>1.00%</x:t>
@@ -433,10 +433,10 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>2,948,798</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$651,861,285.88</x:t>
+    <x:t>2,957,093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$670,047,702.87</x:t>
   </x:si>
   <x:si>
     <x:t>0.96%</x:t>
@@ -451,13 +451,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>12,939,908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$592,388,988.24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.87%</x:t>
+    <x:t>12,976,301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$615,465,956.43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.88%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -469,10 +469,10 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,603,460</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$576,722,441.00</x:t>
+    <x:t>7,624,845</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$588,256,791.75</x:t>
   </x:si>
   <x:si>
     <x:t>0.85%</x:t>
@@ -487,10 +487,10 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,683,516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$354,167,479.92</x:t>
+    <x:t>4,696,690</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$361,363,328.60</x:t>
   </x:si>
   <x:si>
     <x:t>0.52%</x:t>
@@ -502,13 +502,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>43,885,250</x:t>
+    <x:t>43,885,767</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$43,885,249.86</x:t>
+    <x:t>$43,885,766.77</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -520,7 +520,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-12,591,917.01</x:t>
+    <x:t>$-13,231,068.51</x:t>
   </x:si>
   <x:si>
     <x:t>-0.02%</x:t>
@@ -955,7 +955,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9" ht="15" customHeight="1">
@@ -963,28 +963,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="F13" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
+      <x:c r="H13" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9" ht="15" customHeight="1">
@@ -992,28 +992,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9" ht="15" customHeight="1">
@@ -1021,28 +1021,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="F15" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
+      <x:c r="H15" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9" ht="15" customHeight="1">
@@ -1050,28 +1050,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="F16" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
+      <x:c r="H16" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9" ht="15" customHeight="1">
@@ -1079,28 +1079,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
+      <x:c r="F17" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
+      <x:c r="H17" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9" ht="15" customHeight="1">

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-22.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-22.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261021" sheetId="1" r:id="R96d7cebcaaac4ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261021" sheetId="1" r:id="R57bb4da689174b27"/>
   </x:sheets>
 </x:workbook>
 </file>
